--- a/CSV/Ancient City.xlsx
+++ b/CSV/Ancient City.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\friend-zone\XLSX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/CSV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF2CCAC-9844-4114-B3D2-01758C99261A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3A09DA-E683-004D-A0DE-6729AF00C9CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="8370" windowHeight="17385" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
+    <workbookView xWindow="0" yWindow="9620" windowWidth="11480" windowHeight="9980" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,18 +34,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="5">
-  <si>
-    <t>nummer</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>X</t>
   </si>
@@ -53,10 +47,7 @@
     <t>Z</t>
   </si>
   <si>
-    <t>/tp</t>
-  </si>
-  <si>
-    <t>Y</t>
+    <t>Ancient City</t>
   </si>
 </sst>
 </file>
@@ -435,302 +426,195 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="B2">
+        <v>-5656</v>
       </c>
       <c r="C2">
-        <v>-744</v>
-      </c>
-      <c r="D2">
-        <v>-51</v>
-      </c>
-      <c r="E2">
-        <v>-184</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-3000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
+      <c r="B3">
+        <v>-5272</v>
       </c>
       <c r="C3">
-        <v>-5272</v>
-      </c>
-      <c r="D3">
-        <v>-51</v>
-      </c>
-      <c r="E3">
         <v>-2568</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
+      <c r="B4">
+        <v>-4568</v>
       </c>
       <c r="C4">
-        <v>-5656</v>
-      </c>
-      <c r="D4">
-        <v>-51</v>
-      </c>
-      <c r="E4">
-        <v>-3000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>3</v>
+      <c r="B5">
+        <v>-4520</v>
       </c>
       <c r="C5">
-        <v>-4568</v>
-      </c>
-      <c r="D5">
-        <v>-51</v>
-      </c>
-      <c r="E5">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>3</v>
+      <c r="B6">
+        <v>-3816</v>
       </c>
       <c r="C6">
-        <v>-4520</v>
-      </c>
-      <c r="D6">
-        <v>-51</v>
-      </c>
-      <c r="E6">
-        <v>1640</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5816</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>3</v>
+      <c r="B7">
+        <v>-3800</v>
       </c>
       <c r="C7">
-        <v>-3704</v>
-      </c>
-      <c r="D7">
-        <v>-51</v>
-      </c>
-      <c r="E7">
-        <v>5464</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-4856</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>3</v>
+      <c r="B8">
+        <v>-3704</v>
       </c>
       <c r="C8">
-        <v>-3816</v>
-      </c>
-      <c r="D8">
-        <v>-51</v>
-      </c>
-      <c r="E8">
-        <v>5816</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5464</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>3</v>
+      <c r="B9">
+        <v>-2184</v>
       </c>
       <c r="C9">
-        <v>5128</v>
-      </c>
-      <c r="D9">
-        <v>-51</v>
-      </c>
-      <c r="E9">
-        <v>2920</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>3</v>
+      <c r="B10">
+        <v>-1816</v>
       </c>
       <c r="C10">
-        <v>7032</v>
-      </c>
-      <c r="D10">
-        <v>-51</v>
-      </c>
-      <c r="E10">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>3</v>
+      <c r="B11">
+        <v>2824</v>
       </c>
       <c r="C11">
-        <v>7000</v>
-      </c>
-      <c r="D11">
-        <v>-51</v>
-      </c>
-      <c r="E11">
-        <v>-248</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-3320</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>3</v>
+      <c r="B12">
+        <v>2856</v>
       </c>
       <c r="C12">
-        <v>3592</v>
-      </c>
-      <c r="D12">
-        <v>-51</v>
-      </c>
-      <c r="E12">
-        <v>-1800</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-3704</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>3</v>
+      <c r="B13">
+        <v>3592</v>
       </c>
       <c r="C13">
-        <v>3960</v>
-      </c>
-      <c r="D13">
-        <v>-51</v>
-      </c>
-      <c r="E13">
-        <v>-3000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1800</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>3</v>
+      <c r="B14">
+        <v>3928</v>
       </c>
       <c r="C14">
-        <v>3928</v>
-      </c>
-      <c r="D14">
-        <v>-51</v>
-      </c>
-      <c r="E14">
         <v>-2216</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>3</v>
+      <c r="B15">
+        <v>3960</v>
       </c>
       <c r="C15">
-        <v>2856</v>
-      </c>
-      <c r="D15">
-        <v>-51</v>
-      </c>
-      <c r="E15">
-        <v>-3704</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-3000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>3</v>
+      <c r="B16">
+        <v>5128</v>
       </c>
       <c r="C16">
-        <v>2824</v>
-      </c>
-      <c r="D16">
-        <v>-51</v>
-      </c>
-      <c r="E16">
-        <v>-3320</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17">
-        <v>-3800</v>
-      </c>
-      <c r="D17">
-        <v>-51</v>
-      </c>
-      <c r="E17">
-        <v>-4856</v>
+        <v>2920</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}"/>
+  <autoFilter ref="A1:C1" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C17">
+      <sortCondition ref="B1:B17"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/CSV/Ancient City.xlsx
+++ b/CSV/Ancient City.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/CSV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3A09DA-E683-004D-A0DE-6729AF00C9CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A63BAA-E533-284E-9C53-A6C87E1FDC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="9620" windowWidth="11480" windowHeight="9980" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
   </bookViews>
@@ -426,7 +426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -548,10 +548,10 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2824</v>
+        <v>-744</v>
       </c>
       <c r="C11">
-        <v>-3320</v>
+        <v>-184</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -559,10 +559,10 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2856</v>
+        <v>2824</v>
       </c>
       <c r="C12">
-        <v>-3704</v>
+        <v>-3320</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -570,10 +570,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>3592</v>
+        <v>2856</v>
       </c>
       <c r="C13">
-        <v>-1800</v>
+        <v>-3704</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -581,10 +581,10 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>3928</v>
+        <v>3592</v>
       </c>
       <c r="C14">
-        <v>-2216</v>
+        <v>-1800</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -592,10 +592,10 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>3960</v>
+        <v>3928</v>
       </c>
       <c r="C15">
-        <v>-3000</v>
+        <v>-2216</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -603,9 +603,20 @@
         <v>15</v>
       </c>
       <c r="B16">
+        <v>3960</v>
+      </c>
+      <c r="C16">
+        <v>-3000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
         <v>5128</v>
       </c>
-      <c r="C16">
+      <c r="C17">
         <v>2920</v>
       </c>
     </row>
